--- a/data/raw/김포 26년/항공통계상세조회(노선) (3).xlsx
+++ b/data/raw/김포 26년/항공통계상세조회(노선) (3).xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="67">
   <si>
     <t>SEQ</t>
   </si>
@@ -38,13 +38,13 @@
     <t/>
   </si>
   <si>
-    <t>10922</t>
-  </si>
-  <si>
-    <t>1908204</t>
-  </si>
-  <si>
-    <t>17413</t>
+    <t>5459</t>
+  </si>
+  <si>
+    <t>955333</t>
+  </si>
+  <si>
+    <t>8025</t>
   </si>
   <si>
     <t>김포(GMP)</t>
@@ -53,187 +53,166 @@
     <t>간사이(KIX)</t>
   </si>
   <si>
-    <t>620</t>
-  </si>
-  <si>
-    <t>111435</t>
-  </si>
-  <si>
-    <t>1231</t>
+    <t>310</t>
+  </si>
+  <si>
+    <t>56069</t>
+  </si>
+  <si>
+    <t>666</t>
   </si>
   <si>
     <t>광주(KWJ)</t>
   </si>
   <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>6314</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>김해(PUS)</t>
+  </si>
+  <si>
+    <t>712</t>
+  </si>
+  <si>
+    <t>103956</t>
+  </si>
+  <si>
+    <t>364</t>
+  </si>
+  <si>
+    <t>나고야(NGO)</t>
+  </si>
+  <si>
+    <t>10860</t>
+  </si>
+  <si>
+    <t>133</t>
+  </si>
+  <si>
+    <t>다싱(PKX)</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>5351</t>
+  </si>
+  <si>
+    <t>98</t>
+  </si>
+  <si>
+    <t>도쿄 하네다(HND)</t>
+  </si>
+  <si>
+    <t>372</t>
+  </si>
+  <si>
+    <t>86479</t>
+  </si>
+  <si>
+    <t>2202</t>
+  </si>
+  <si>
+    <t>북경(PEK)</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>12970</t>
+  </si>
+  <si>
+    <t>160</t>
+  </si>
+  <si>
+    <t>사천(HIN)</t>
+  </si>
+  <si>
+    <t>7158</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>쑹산(TSA)</t>
+  </si>
+  <si>
+    <t>10630</t>
+  </si>
+  <si>
+    <t>144</t>
+  </si>
+  <si>
+    <t>여수(RSU)</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>10416</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>울산(USN)</t>
+  </si>
+  <si>
+    <t>10213</t>
+  </si>
+  <si>
+    <t>제주(CJU)</t>
+  </si>
+  <si>
+    <t>3302</t>
+  </si>
+  <si>
+    <t>598319</t>
+  </si>
+  <si>
+    <t>3751</t>
+  </si>
+  <si>
+    <t>카오슝(KHH)</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>8716</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>포항 경주(KPO)</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>1972</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>홍차오(SHA)</t>
+  </si>
+  <si>
     <t>124</t>
   </si>
   <si>
-    <t>13143</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>김해(PUS)</t>
-  </si>
-  <si>
-    <t>1427</t>
-  </si>
-  <si>
-    <t>209481</t>
-  </si>
-  <si>
-    <t>750</t>
-  </si>
-  <si>
-    <t>나고야(NGO)</t>
-  </si>
-  <si>
-    <t>21197</t>
-  </si>
-  <si>
-    <t>221</t>
-  </si>
-  <si>
-    <t>다싱(PKX)</t>
-  </si>
-  <si>
-    <t>62</t>
-  </si>
-  <si>
-    <t>11108</t>
-  </si>
-  <si>
-    <t>172</t>
-  </si>
-  <si>
-    <t>도쿄 하네다(HND)</t>
-  </si>
-  <si>
-    <t>744</t>
-  </si>
-  <si>
-    <t>170117</t>
-  </si>
-  <si>
-    <t>3160</t>
-  </si>
-  <si>
-    <t>북경(PEK)</t>
-  </si>
-  <si>
-    <t>186</t>
-  </si>
-  <si>
-    <t>28203</t>
-  </si>
-  <si>
-    <t>337</t>
-  </si>
-  <si>
-    <t>사천(HIN)</t>
-  </si>
-  <si>
-    <t>14562</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>쑹산(TSA)</t>
-  </si>
-  <si>
-    <t>21357</t>
-  </si>
-  <si>
-    <t>270</t>
-  </si>
-  <si>
-    <t>여수(RSU)</t>
-  </si>
-  <si>
-    <t>184</t>
-  </si>
-  <si>
-    <t>21787</t>
-  </si>
-  <si>
-    <t>64</t>
-  </si>
-  <si>
-    <t>울산(USN)</t>
-  </si>
-  <si>
-    <t>20778</t>
-  </si>
-  <si>
-    <t>58</t>
-  </si>
-  <si>
-    <t>제주(CJU)</t>
-  </si>
-  <si>
-    <t>6602</t>
-  </si>
-  <si>
-    <t>1189621</t>
-  </si>
-  <si>
-    <t>9957</t>
-  </si>
-  <si>
-    <t>청도(TAO)</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>164</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>카오슝(KHH)</t>
-  </si>
-  <si>
-    <t>104</t>
-  </si>
-  <si>
-    <t>17875</t>
-  </si>
-  <si>
-    <t>210</t>
-  </si>
-  <si>
-    <t>타크빌라란(TAG)</t>
-  </si>
-  <si>
-    <t>161</t>
-  </si>
-  <si>
-    <t>포항 경주(KPO)</t>
-  </si>
-  <si>
-    <t>61</t>
-  </si>
-  <si>
-    <t>4108</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>홍차오(SHA)</t>
-  </si>
-  <si>
-    <t>248</t>
-  </si>
-  <si>
-    <t>53107</t>
-  </si>
-  <si>
-    <t>912</t>
+    <t>25910</t>
+  </si>
+  <si>
+    <t>302</t>
   </si>
 </sst>
 </file>
@@ -284,7 +263,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="30"/>
   <sheetData>
     <row r="1">
@@ -544,7 +523,7 @@
         <v>50</v>
       </c>
       <c r="F13" t="s" s="0">
-        <v>51</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14">
@@ -555,16 +534,16 @@
         <v>11</v>
       </c>
       <c r="C14" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="D14" t="s" s="0">
         <v>52</v>
       </c>
-      <c r="D14" t="s" s="0">
+      <c r="E14" t="s" s="0">
         <v>53</v>
       </c>
-      <c r="E14" t="s" s="0">
+      <c r="F14" t="s" s="0">
         <v>54</v>
-      </c>
-      <c r="F14" t="s" s="0">
-        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -575,16 +554,16 @@
         <v>11</v>
       </c>
       <c r="C15" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="D15" t="s" s="0">
         <v>56</v>
       </c>
-      <c r="D15" t="s" s="0">
+      <c r="E15" t="s" s="0">
         <v>57</v>
       </c>
-      <c r="E15" t="s" s="0">
+      <c r="F15" t="s" s="0">
         <v>58</v>
-      </c>
-      <c r="F15" t="s" s="0">
-        <v>59</v>
       </c>
     </row>
     <row r="16">
@@ -595,16 +574,16 @@
         <v>11</v>
       </c>
       <c r="C16" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="D16" t="s" s="0">
         <v>60</v>
       </c>
-      <c r="D16" t="s" s="0">
+      <c r="E16" t="s" s="0">
         <v>61</v>
       </c>
-      <c r="E16" t="s" s="0">
+      <c r="F16" t="s" s="0">
         <v>62</v>
-      </c>
-      <c r="F16" t="s" s="0">
-        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -615,56 +594,16 @@
         <v>11</v>
       </c>
       <c r="C17" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="D17" t="s" s="0">
         <v>64</v>
-      </c>
-      <c r="D17" t="s" s="0">
-        <v>57</v>
       </c>
       <c r="E17" t="s" s="0">
         <v>65</v>
       </c>
       <c r="F17" t="s" s="0">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n" s="0">
-        <v>16.0</v>
-      </c>
-      <c r="B18" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="C18" t="s" s="0">
         <v>66</v>
-      </c>
-      <c r="D18" t="s" s="0">
-        <v>67</v>
-      </c>
-      <c r="E18" t="s" s="0">
-        <v>68</v>
-      </c>
-      <c r="F18" t="s" s="0">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n" s="0">
-        <v>17.0</v>
-      </c>
-      <c r="B19" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="C19" t="s" s="0">
-        <v>70</v>
-      </c>
-      <c r="D19" t="s" s="0">
-        <v>71</v>
-      </c>
-      <c r="E19" t="s" s="0">
-        <v>72</v>
-      </c>
-      <c r="F19" t="s" s="0">
-        <v>73</v>
       </c>
     </row>
   </sheetData>
